--- a/Gulf_Dashboard_W32_2026.xlsx
+++ b/Gulf_Dashboard_W32_2026.xlsx
@@ -491,50 +491,34 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>8.4 SHE NCR Status
-Doc No. Description Issue date Root cause Status
-14 PRO [Elec.] Submission of revised TBE for MV, LV SWGR &amp; MCC, PDP, ATS, Busduct, CSCS_T1 11 August, 2026
-15 PRO [Inst.] Submission of TBE for Waste Water Management System_R0 11 August, 2026
-18 CON [LNG Tank] Commencement of Roof Plate Installation for LNG Tank 102 6 August, 2026
-19 CON [BOP &amp; Utility] Commencement of Pile Cutting and Lean Concrete Work for Warehouse Building 7 August, 2026
-20 CON [BOP &amp; Utility] Completion of Foundation Work for Maintenance Building 8 August, 2026
-21 CON [BOP &amp; Utility] Completion of Foundation Work for Water Storage Tank 12 August, 2026
-Discipline Plan &amp; Actual Approval &amp; Review / Information Construction
-Total This Week Accum. Total This Week Accum.
-Plan 0 29 0 20
-General 35 35 34
-Actual 0 29 0 21
-Plan 0 107 0 80
-Process 115 115 93
-Actual 0 107 0 85
-Plan 0 76 0 73
-Mechanical 77 77 77
-Actual 0 76 0 74
-Plan 0 113 2 100</t>
+          <t>ISB Elevator — Application of elevator in instrument / substation building should be settled considering construction schedule.
+Duct Bank for Future GTG Power Line — Confirmation on duct bank for future GTG power line installation is required.
+Painting Specification (Color) — Review result to be required quickly for proceeding further.
+Trolley Beam and Gondola for LNG Tanks — Considering the safe work and maintenance, it is suggested not to install trolley beam</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>- GMTP/PMC/PCC Mass TBT was cancelled due to Thai Mother’s Day.
-- SHE/EIA weekly audit was cancelled due to Thai Mother’s Day.
-- Big cleaning day on 8 Aug 2026.
-- Knot Tying Training for Work at Height (WAH)on 6 Aug 2026. - GMTP/PMC/PCC management TBT and safety award on 19 Aug 2026.
-- Basic Fire Fighting Training was held on 10-11 Aug 2026. - SHE/EIA weekly audit on 19 Aug 2026.
-- Demonstration of Roof Plate Installation at T-101 on 10 Aug 2026. - Big cleaning day every Saturday
-- Roof plate installation at T-101 on 12 Aug 2026.
-Security Security
-- Strictly control personnel and vehicle gate pass, check the entrance and exit of materials and - Provided temporary security guard for control personal, vehicle and material at site main gate 24 hours.
-equipment into and out of the projectarea 24/7.(Night shift patrols every 1 hour)
-EIA/EHIA EIA/EHIA
-- CNT Worker camp audit with Pha Yoon Community Leader on 19 Aug 2026.
-- Hazardous waste disposal on 8 Aug 2026
-- Mass concrete pouring for Tank wall on 17 and 19 Aug 2026.
-- Sampling Coastal Water Quality (Suspended Solids) on 12 Aug 2026.
-Issue for Issue for Document Class
-Approval Construction Z X Y
-General 0 0 0 0 0
-Process 0 0 0 0 0
-Mechanical 0 0 0 0 0</t>
+          <t>[LNG Tank] Tank 101: Installation DOKA (outer wall 6th) climbing form
+[LNG Tank] Tank 101: Wall rebar pre-fabrication and installation work for outer wall 6th
+[LNG Tank] Tank 101: Insert plate installation and Post-tensioning Work for outer wall 6th
+[LNG Tank] Tank 101: Pouring Concrete for outer wall 6th (19.Aug)
+[LNG Tank] Tank 102: Wall rebar pre-fabrication and installation work for outer wall 5th
+[LNG Tank] Tank 102: Post- tensioning Work for outer wall 5th
+[LNG Tank] Tank 102: Pouring Concrete for outer wall 5th (17.Aug)
+[LNG Tank] Tank 101: Purlin Welding &amp; Grinding
+[LNG Tank] Tank 101: Roof Plate arrangement
+[LNG Tank] Tank 102: Purlin Welding &amp; Grinding
+[LNG Tank] Tank 102: Roof Plate arrangement
+[LNG Tank] Shop Area: Compression Ring Fabrication
+[BOP Area] UG Piping Work: Excavation and Backfill work
+[BOP Area] UG Piping Work: Field Fusion Weld work
+[BOP Area] UG Piping Work: Pouring Con’c for Valve Box wall
+[BOP Area] UG Piping Work: GRP lamination work
+[BOP Area] Piperack – B, C, D, E: Excavation work for FDN
+[BOP Area] Piperack – B, C, D, E: Rebar, Formwork and Concrete Work for Foundation, PC Frame and Longi. Beam
+[BOP Area] Piperack – B, C, D, E: Piperack B/C Main Frame &amp; Longi Beam erection work
+[BOP Area] Piling Work: Pile Driving at Process Area</t>
         </is>
       </c>
     </row>

--- a/Gulf_Dashboard_W32_2026.xlsx
+++ b/Gulf_Dashboard_W32_2026.xlsx
@@ -546,7 +546,27 @@
 [115kV Transmission Line (PEA, FEC)] Relocate water pipe along the road of Department of Rural Roads</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr"/>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>[PV Farm (GUE)] Install Mounting Structure 567 of 768 table, 10 Construction inspected 314 table, 40.89%.
+[PV Farm (GUE)] Install PV Module 31,577 of 84,500 ea, 37.37%. 0 Jan
+[PV Farm (GUE)] Laying DC cable 243,238 of 320,000 m, 76.01%.
+[PV Farm (GUE)] Laying LV cable 10,693 of 30,050 m, 35.58%.
+[PV Farm (GUE)] Install Inverter 136 of 149 nos, 91.27%.
+[Substation (SIEMENS)] Substation &amp; Control Building : Progress Execu Installed switchgear, installed cable ladder.
+[Substation (SIEMENS)] Switchyard : Continued Individual test.
+[Substation (SIEMENS)] Office Building : Installed roof structure, started masonry work.
+[Substation (SIEMENS)] Store Building : Started masonry work.
+[Substation (SIEMENS)] Guardhouse : No activities
+[115kV Transmission Line (PEA, FEC)] Construct foundation 559 of 748 tive Summa nos.
+[115kV Transmission Line (PEA, FEC)] Installed concrete pole 552 of 744 nos.
+[115kV Transmission Line (PEA, FEC)] Installed top pole 501 of 744 nos.
+[Communication / Fiber (กบศ, ITL)] Under review drawing by ry as EGAT.
+[Communication / Fiber (กบศ, ITL)] Under revise drawing cross section of road.
+[Communication / Fiber (กบศ, ITL)] Continued HDD work at railway’s area.
+[Communication / Fiber (กบศ, ITL)] Plan to deliver panel on 03- Aug-26.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -578,7 +598,25 @@
 [Communication / Fiber (PEA, JANUS)] Awaiting 115kV Transmission Line HDD work completion and concrete pole installation to proceed with fiber optic cable pulling.</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr"/>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>[PV Farm (GUE)] Piling work PV areas T10 Constru
+[PV Farm (GUE)] Install PV mounting, PV Module, RMU Panel. Underground LV cable and MV cable installation. 10 Jan
+[PV Farm (GUE)] Unit Substation : Rebar &amp; formwork installation and Concrete pouring. And Cable ladder installation.
+[Substation (SIEMENS)] Install Support Cable trench. ction Progres
+[Substation (SIEMENS)] Switchyard Aluminium and Bus Fitting installation.
+[Substation (SIEMENS)] Brick Wall Installation for Control Building.
+[Substation (SIEMENS)] Ground grid System Installation.
+[Substation (SIEMENS)] MV Switchgear installation.
+[115kV Transmission line (PEA, FEC)] Civil work : Foundation work, Concrete pole s Executive installation and Install Manhole.
+[115kV Transmission line (PEA, FEC)] Electrical work : Top pole installation, Cable pulling for UG, Cable splicing and Cable stringing.
+[Add Bay (PEA, FEC)] Aluminum Tube Welding and Installation Summary a
+[Add Bay (PEA, FEC)] RSC and HDPE Conduit installation
+[Add Bay (PEA, FEC)] Control Cable pulling
+[Add Bay (PEA, FEC)] Install Cable ladder
+[Communication / Fiber (PEA, JANUS)] Drawing approval. s</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -603,7 +641,30 @@
 [115 kV Transmission line (PEA, FEC)] To expedite the mobilization of the additional manpower for the Civil works.</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr"/>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>[PV Farm (GUE)] Civil work:
+[PV Farm (GUE)] Unit substation: Late plan100.00% vs Actual 70.29% (Delayed -29.71%).
+[PV Farm (GUE)] Road work: Crushed stone leveling and compaction.
+[PV Farm (GUE)] Electrical work:
+[PV Farm (GUE)] PV mounting installation: 1,275/1,342 tables., (95.01%)
+[PV Farm (GUE)] PV module installation: 119,078/126,750 panels., (93.95%)
+[PV Farm (GUE)] PV inverter installation: 203/222 Nos., (91.44%)
+[PV Farm (GUE)] DC cable installation: 388,995/402,880 m., (96.55%)
+[PV Farm (GUE)] LV cable installation: 30,892/32,254 m., (95.78%)
+[PV Farm (GUE)] MV cable installation: 17,058/18,840 m., (90.54%)
+[PV Farm (GUE)] ACCB installation: 22/22 Nos., (100.00%)
+[PV Farm (GUE)] RMU installation: 12/12 Nos., (100.00%)
+[PV Farm (GUE)] Transformer SAT: 12/12 Ea.,(100.00%)
+[Substation (SIEMENS)] Civil work:
+[Substation (SIEMENS)] Control building: Wall paint and Vinyl installation.
+[Substation (SIEMENS)] Office building: Concrete pouring for roof beam.
+[Substation (SIEMENS)] Store and guardhouse: Roof structure installation.
+[Substation (SIEMENS)] Drainage: Earth work and RC pipe installation.
+[Substation (SIEMENS)] Cable trench: Concrete work for wall.
+[Substation (SIEMENS)] Fence: Rebar and formwork installation.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -622,7 +683,17 @@
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr"/>
-      <c r="E6" s="2" t="inlineStr"/>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>[PVfarm(GUE)] PQ test completed
+[PVfarm(GUE)] kV control test with EGAT Completed
+[PVfarm(GUE)] Joint test completed
+[PVfarm(GUE)] Continue to grass cutting and PV cleaning work
+[115kVSubstation (SIEMENS)] Handover spare parts completed
+[115kVSubstation (SIEMENS)] Rectifying punch list
+[TransmissionLine and Fiber optic (PEA)] Inter trip and tele protection test completed</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -641,7 +712,22 @@
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr"/>
-      <c r="E7" s="2" t="inlineStr"/>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>[PVfarm(GUE)] Grass planting works.
+[PVfarm(GUE)] Continue Lighting system installation
+[PVfarm(GUE)] Continue MCC walk down and Close punch.
+[PVfarm(GUE)] Continue Fiber optic cable pulling works for Boundary CCTV
+[PVfarm(GUE)] Installation Pump water tank
+[PVfarm(GUE)] Continue Drainage system work
+[PVfarm(GUE)] Continue Grass cutting PV Farm.
+[PVfarm(GUE)] Continue Cleaning PV modules
+[PVfarm(GUE)] Continue Concrete pouring pavement at BESS area
+[PVfarm(GUE)] Thermoscan at equipment.
+[PVfarm(GUE)] Sound test at equipment.
+[115kVSubstation(SIEMENS)] Continue close punch MCC.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -667,26 +753,26 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Civil work Civil work
-➢ Matal sheet installation RMU Station. ➢ Matal sheet installation RMU Station.
-➢ Water tank storage installation completed.
-Electrical work
-Electrical work ➢ Mounting and PV panel installation.
-➢ Mounting and PV panel installation. ➢ MV Cable installation completed.
-➢ MV Cable installation. ➢ Cable test and IV Curve test.
-➢ Cable test and IV Curve test. ➢ LV cable pulling BESS area.
-➢ LV cable pulling BESS area. ➢ Control cable pulling BESS and TR station.
-➢ Control cable pulling BESS and TR station. ➢ Fiber optic installation.
-➢ Fiber optic installation.
-➢ MCC walkdown civil work. ➢ MCC walkdown.
-➢ Start grass installation. ➢ Grass installation.
-Electrical work Electrical work
-➢ Power transformer function test completed. ➢ Function test ACDB.
-➢ 115kV Relay protection setting and test. ➢ Ground continuity test.
-➢ Function &amp; interlocking test 115kV, 22kV system ➢ Torque check power cable.
-➢ SCADA system start up config completed.
-➢ SCADA system start up config.
-➢ Concrete foundation installation. ➢ Concrete foundation installation.</t>
+          <t>[PV farm (GPD)] Matal sheet installation RMU Station.
+[PV farm (GPD)] Mounting and PV panel installation.
+[PV farm (GPD)] MV Cable installation completed.
+[PV farm (GPD)] Cable test and IV Curve test.
+[PV farm (GPD)] LV cable pulling BESS area.
+[PV farm (GPD)] Control cable pulling BESS and TR station.
+[PV farm (GPD)] Fiber optic installation.
+[Substation (SIEMENS)] MCC walkdown.
+[Substation (SIEMENS)] Grass installation.
+[Substation (SIEMENS)] Function test ACDB.
+[Substation (SIEMENS)] Ground continuity test.
+[Substation (SIEMENS)] Torque check power cable.
+[Substation (SIEMENS)] SCADA system start up config completed.
+[Transmission Line (PEA&amp;TEC)] Concrete foundation installation.
+[Transmission Line (PEA&amp;TEC)] Manhole installation.
+[Transmission Line (PEA&amp;TEC)] Foundation Steel Tower.
+[Transmission Line (PEA&amp;TEC)] Top pole assembly installation.
+[Transmission Line (PEA&amp;TEC)] Stringing AAC 400 Sq.mm. and OHGW.
+[Transmission Line (PEA&amp;TEC)] Underground cable onsite.
+[Transmission Line (PEA&amp;TEC)] Assembly steel tower.</t>
         </is>
       </c>
     </row>
@@ -753,26 +839,22 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>➢ Continue Cut and Fill for Subgrade layer and Subbase layer Central A, Central B ,Service Road and South
-➢ Continue Pipe and Box culvert South ,Central A ,North A and Service Road
-➢ Continue 33kV Pole Installation
-Actual Completed Deviation
-Fri Sat Sun Mon Tue Wed Thu Fri Sat Sun Mon Tue Wed Thu Fri Sat Sun Mon Tue Wed Thu Fri Sat Sun Mon Tue Wed Thu
-Start Finish
-7/31 8/1 8/2 8/3 8/4 8/5 8/6 8/7 8/8 8/9 8/10 8/11 8/12 8/13 8/14 8/15 8/16 8/17 8/18 8/19 8/20 8/21 8/22 8/23 8/24 8/25 8/26 8/27
-1 North A ( STA.1+400 - STA.4+667 )
-Plan 15-May 16-Aug 7.5% 7.5% 7.5% 7.5% 7.5% 7.5% 5% 7.5% 7.5% 7.5% 7.5% 7.5% 7.5% 5% 7.5% 7.5% 7.5% 7.5% 7.5% 7.5% 5%
-1 DRAINAGE SYSYTEM ( PIPE &amp; BOX CULVERT )
-Actual 15-May 25.0% -25.0% 2.5% 5% 2.5% 2.5% 0.0% 5% 2.5% 2.5% 2.5% 2.5% 5% 5% 0% 8%
-Plan 7-Aug 20-Aug 7.5% 7.5% 7.5% 7.5% 7.5% 7.5% 5% 7.5% 7.5% 7.5% 7.5% 7.5% 7.5% 5%
-2 FILL COMPACTED BASE COURSE STA.1+400 - STA.2+000
-Actual 7-Aug 30.0% -20.0% 5% 5% 5% 5% 5% 0% 5%
-3 FILL COMPACTED BASE COURSE STA.2+000 - STA.2+500
-Plan 14-Aug 27-Aug 7.5% 7.5% 7.5% 7.5% 7.5% 7.5% 5% 7.5% 7.5% 7.5% 7.5% 7.5% 7.5% 5%
-4 FILL COMPACTED BASE COURSE STA.2+500 - STA.3+000
-Actual 14-Aug 0.0% 0.0%
-Plan 14-Aug 23-Jul 7.5% 7.5% 7.5% 7.5% 7.5% 7.5% 5% 7.5% 7.5% 7.5% 7.5% 7.5% 7.5% 5%
-5 FILL COMPACTED BASE COURSE STA.3+000 - STA.3+500</t>
+          <t>[CBOP (PCZ)] Subgrade = 18,132/18,925 (95.81%)
+[CBOP (PCZ)] Subbase = 16,395/18,925 (86.63%)
+[CBOP (PCZ)] Pipe and Box culvert Ongoing = 15 Completed =6/37
+[CBOP (PCZ)] 33 kV Pole (12.20) = 430/832(51.13%)
+[TSA (GOLD WIND)] Excavation for Hardstand Ongoing = 10 Completed =3/14
+[TSA (GOLD WIND)] Excavation for Foundation Ongoing = 5 Completed =5/14
+[TSA (GOLD WIND)] Lean Concrete Completed =4/14
+[TSA (GOLD WIND)] Rebar Ongoing = 4 Completed =0/14
+[Substation (SIEMENS)] Foundation Work for Substation Control Building : Ongoing
+[T &amp; L (ENCOM, INTERLINK)] Concrete FD = 290/439(66.06%)
+[T &amp; L (ENCOM, INTERLINK)] Concrete Pole=221/466(47.42%)
+[Terminal Substation (กบศ, DEMCO)] Ground Grid : 98.00%
+[Terminal Substation (กบศ, DEMCO)] Roadwork : 80.00%
+[Terminal Substation (กบศ, DEMCO)] Fence Work : 80.00%
+[Terminal Substation (กบศ, DEMCO)] Drainage system : 95.00 %
+[Terminal Substation (กบศ, DEMCO)] Electrical Work : 95.60%</t>
         </is>
       </c>
     </row>
@@ -795,25 +877,24 @@
       <c r="D12" s="2" t="inlineStr"/>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>➢ Continue to road base course compaction work.
-➢ Continue to excavation and installation for 33kV Pole.
-➢ Continue to excavation work for drainage system.
-➢ Continue to excavation work.
-➢ Continue to rebar installation.
-➢ Plan to pouring concrete for WTG-03 next week.
-➢ Continue to site preparation (Earth Work).
-➢ Continue to excavation for foundation at SWYD area.
-➢ Continue to 115kV foundation rebar installation.
-➢ Continue to backfilling work at substation area.
-➢ Continue to foundation work
-➢ Continue to cable Stringing work.
-➢ Continue foundation excavation work.
-➢ Continue to pole installation
-potential hazards and ensure workers understood the work scope. potential hazards, and ensure compliance with safety requirements.
-activities.
-Alcohol level screening for employees entering the project site to Installation of rebar caps on exposed reinforcement bars to prevent
-Install No Unauthorized Entry Signs in Restricted Areas.
-prevent work-related hazards and ensure safe operations. impalement hazards.</t>
+          <t>[CBOP (PCZ)] Continue to road base course compaction work.
+[CBOP (PCZ)] Continue to excavation and installation for 33kV Pole.
+[CBOP (PCZ)] Continue to slope erosion control work.
+[CBOP (PCZ)] Continue to side ditch work.
+[TSA (Goldwind)] Continue to excavation work at WTG-08, WTG- 10, WTG-11, WTG-12, WTG-13.
+[TSA (Goldwind)] Continue to rebar installation at WTG-03, WTG- 04, WTG-06, WTG-14.
+[TSA (Goldwind)] Soil improvement at WTG-05.
+[TSA (Goldwind)] Continue to soil backfilling at WTG-01.
+[TSA (Goldwind)] Pouring lean concrete at WTG-05
+[Substation (SIEMENS)] Continue to site preparation (Earth Work).
+[Substation (SIEMENS)] Continue to backfilling work at substation area.
+[Substation (SIEMENS)] Excavation for foundation work.
+[Substation (SIEMENS)] Pouring concrete equipment foundation.
+[Substation (SIEMENS)] Pouring lean concrete transformer foundation.
+[Transmission Line (ENCOM/RSS2016)] Continue to foundation work.
+[Transmission Line (ENCOM/RSS2016)] Continue to top pole equipment installation.
+[Transmission Line (ENCOM/RSS2016)] Continue to cable Stringing work.
+[Transmission Line (ENCOM/RSS2016)] Continue to pole installation.</t>
         </is>
       </c>
     </row>
@@ -842,26 +923,16 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-Plant grass for erosion control. -Concrete pole 33kV installation.
--Excavation earth ditch.
-Bridge and Box culvert works
--Bridge NO.05,06 :concrete pouring.
--Bridge NO.02A pile driving pier 2,3.
--RC pipe culvert installation.
-Acc.Plan Last Week Acc.Plan Last Week Acc. Plan
-Acc.Actual Last Week as of Plan this week Plan this week Acc. Plan (Contract BL) Acc. Actual this week as
-(Contract BL) (Execution Plan) Delay/Ahead Progress this week (Execution Plan) Delay/Ahead
-No. Work Task %W.V. 06 Aug 26 (Contract BL) (Execution Plan) as of 13 Aug 26 of 13 Aug 26
-as of 06 Aug 26 as of 06 Aug 26 [B] - [C] of 13 Aug 26 as of 13 Aug 26 [B] - [C]
-[B] as of 13 Aug 26 as of 13 Aug 26 [A] [B]
-[A] [C] [C]
-1 ENGINEERING WORK 5.00% 95.33% 55.88% 54.02% -1.85% 1.15% 1.16% 0.77% 96.48% 57.04% 54.79% -2.25%
-2 PROCUREMENT WORK 55.00% 46.29% 35.40% 35.40% 0.00% 0.72% 0.00% 0.00% 47.01% 35.40% 35.40% 0.00%
-3 CONSTRUCTION WORK 30.00% 9.00% 4.52% 3.78% -0.74% 0.41% 0.51% 0.41% 9.41% 5.03% 4.19% -0.85%
-4 COMMISSIONING WORK 10.00% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00%
-Overall Progress 32.92% 23.62% 23.30% -0.31% 0.58% 0.21% 0.16% 33.50% 23.83% 23.47% -0.36%
-➢ Excavation work for WTG-01, WTG-05.
-➢ Piling work for WTG-02.</t>
+          <t>[TSA (Goldwind)] Excavation work for WTG-01, WTG-05.
+[TSA (Goldwind)] Completed piling work for WTG-04.
+[TSA (Goldwind)] Soil improvement WTG-03,WTG-04.
+[CBOP (PCZ)] Road work
+[CBOP (PCZ)] Excavation earth ditch. Bridge and Box culvert
+[CBOP (PCZ)] Soil backfill for Box Culvert No. 08.
+[CBOP (PCZ)] Bridge NO.05,06 Installation plank girders.
+[CBOP (PCZ)] Bridge NO.02A Pile driving work.
+[CBOP (PCZ)] Bridge NO.10 Pile driving work. Electrical
+[CBOP (PCZ)] Concrete pole 33kV installation.</t>
         </is>
       </c>
     </row>
@@ -886,30 +957,7 @@
           <t>GCE-001-C-010-UOO-001 General Plant Layout General Layout The distance of the stormwater retention pond from the property boundary does not comply with the Excavation and Land Filling Act B.E. 2543</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Safety &amp; Health:
-Management site walkdown
-Toolbox talk activity
-Safety induction training to new contractors​
-Weekly Inspect Safety​
-Weekly Random Alc. Test
-Environment &amp; CoP:
-Road cleaning (Campsite STECON/IEAT Road)
-Water spray to reduce dust
-Monitor noise during overtime work
-Activities CC/SC (*)
-Plan % Actual % Diff. % Plan % Actual % Diff. % Acc.Plan %
-Engineering 10.00% 92.82% 60.96% -31.86% 93.44% 62.29% -31.15% 94.92%
-Procurement 40.00% 82.61% 79.02% -3.58% 84.27% 79.50% -4.77% 85.67%
-Construction 40.00% 22.90% 16.04% -6.86% 25.06% 16.54% -8.52% 27.18%
-Commissioning 10.00% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00%
-Overall 100.00% 51.49% 44.12% -7.36% 53.08% 44.64% -8.44% 54.63%
-** The data cut off every Friday of week
-** Engineering delay from O &amp; M Manual, Shop Test Report , Shop ITP,DCS System
-** Procurement Delay from Manufacturing STG foundation anchor bolts, condenser metal sheet</t>
-        </is>
-      </c>
+      <c r="E14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -932,31 +980,16 @@
           <t>Detail and spec of equipment at riser pole for PEA approval.
 Detail drawing of water pond.
 Detail drawing of pump foundation at cooling, service water pump
-Detail drawing of foundation and architecture of BOP building</t>
+Detail drawing of foundation and architecture of BOP building
+Detail of underground pipe of toilet at steam turbine building.</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Activities CC/SC (*)
-Plan% Actual% Diff.% Plan% Actual% Diff.% Acc. Plan%
-Engineering 10% 92.82% 60.98% -31.84% 93.44% 62.41% -31.03% 94.92%
-Procurement 40% 82.61% 79.02% -3.59% 84.27% 79.50% -4.77% 85.67%
-Construction 40% 22.90% 17.70% -5.20% 25.06% 18.06% -7.00% 27.18%
-Commissioning 10% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00%
-Overall 100% 51.49% 44.79% -6.70% 53.08% 45.26% -7.82% 54.63%
-5 Maximum Quantity of Heavy Machinery at Site Inspection as period
-and keep related document
-6 Summary of SHE Weekly Audit issues Walk down
-- This week (Finished : 13, Remaining : 0)
-- Total (Finished : 83, Remaining : 0)
-0 RFC , 3 NCR
-7 Stakeholder Engagement Plan Continue as plan
-8 SHE Plan for counting manpower working at site Manpower daily report have started to generating automatically at 7:00
-AM everyday by e-mail
-9 Status of EPC Foreigner staff and worker personal mandatory document Pending has plan to finish &lt;31 Aug 2026&gt;
-Safety &amp; Health:
-• Safety Toolbox Talk before starting work and Mass Toolbox Talk and counting manpower
-• Safety training for newcomer</t>
+          <t>Pouring concrete from EL.+5.45 to El.+8.00
+Boiler : Install middle part and upper part structure Z5-Z6
+FGT area: Install structure
+STG :Installation rebar, form work and pouring concrete for 2nd floor</t>
         </is>
       </c>
     </row>
@@ -976,52 +1009,16 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>311-314 Refuse Bunker Super structure up to 35.5m elevation 9 May 26 23 Nov 26 Delay progress
-325-326 Tipping hall Foundation up to ground (Include piling work) 1 Feb 26 9 Jul 26 8 Feb 26 On going Delay finish
-327 Tipping hall Super structure up to 13m elevation 10 Jul 26 19 Oct 26 Deley start
-330-335 Boiler Island &amp; Auxiliary Equipment Foundation 5 Nov 25 14 Jul 26 8 Jan 26 On going
-346 Steam Turbine Generator &amp; Electrical Construction 18 Feb 26 3 Mar 27 8 Feb 26 On going
-408 Holding Pond and Emergency Pond Construction 23 May 26 20 Nov 26
-14 Boiler Arrival at site 12 Jun 26 12 Jun 26 3 May 26 20 Jun 26 Completed
-11 Incinerator Arrival at site 8 May 26 8 May 26 3 May 26 5 May 26 Completed
-15 Steam turbine Arrival at site 2 Oct 26 2 Oct 26
-62- Producing qualified water (Water Receiving date) 23 Feb 27 8 Mar 27
-Area Work Description Target Date Problem
-Direct discuss with director/SM of STECON for
-Concrete ground slab for fire water pump support manpower
-21 Aug 2026
-BOP 1. STECON will add more 30 people for bunkers
-and surroundings.
-Foundation for service water &amp; cooling tower
-07 Sep 2026 2. Invite local leader to discuss with STECON for
-makeup pumps
-manpower supply.</t>
-        </is>
-      </c>
+      <c r="D16" s="2" t="inlineStr"/>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>(7th Jul 2026) (14thAug 2026)
-Activities CC/SC(*)
-Plan Actual Diff. Plan Actual Diff. Acc.Plan
-% % % % % % %
-Engineering 10% 93.75% 62.06% -31.69% 94.23% 63.25% -30.98% 95.68%
-Procurement 40% 87.53% 80.40% -7.13% 88.85% 80.77% -8.08% 88.83%
-Construction 40% 27.12% 21.54% -5.58% 28.97% 22.47% -6.50% 28.97%
-Commissioning 10% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00%
-Overall 100% 55.23% 46.98% -8.25% 56.55% 47.62% -8.93% 58.06%
-On Schedule A BitDelay Big Delay EPC has adjusted the PMS to Rev.Hto make the plan consistent with the actual work.
-(0.00% or more) (-0.01% to –4.99%) (-5.00% or more)
-Safety &amp; Health
-• Management Weekly Route Walk - Every Tuesday
-• Weekly ESH Meeting - Every Tuesday
-• Weekly Project Meeting with - Every Tuesday
-• Toolbox Talk - Everyday before working
-• Safety training (if any)
-• Inspect equipment before working (Daily)
-• Random test alcohol
-Environment &amp; CoP</t>
+          <t>Bunker building: Concrete pouring for Lift 4 Wall EL +8.00 to +12.45 m. (22 Aug 2026)
+Tipping hall: Completion of concrete pouring for ground slab
+Boiler Erection: Completion of water wall by (30 Aug 26)
+FGT: Completionof installation Spray Reaction tower by 4 Sep 26 and Bag filer house by (1 Sep 26)
+STG &amp; ECB: Completion of concrete pouring for column (EL -0.7 to +3.75 m.) 27 column (31 Jul 26) Completion of flat slab (EL +3.75 m.) (30 Aug 26)
+BOP: Completion of ground slab for fire water pump shelter (21 Aug 26) BOP:Completion of foundation service water pump and cooling tower makeup pump (7 Sep 26)
+Manhole and duct bank: Completion of Manhole and duct bank for priority 1 (8 Oct 26)</t>
         </is>
       </c>
     </row>
@@ -1043,31 +1040,16 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Skill manpower shortage e.g. fitter, piping welder</t>
+          <t>Skill manpower shortage e.g. fitter, piping welder
+Recommend spare part list
+Isometric drawing of fire fighting system (U/G and A/G).
+Pipe support standard drawing from CEEC.</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>(07 Aug 26 (14 Aug 26)
-Activities CC/SC (*)
-Plan Actual Diff. Plan Actual Diff. Acc.Plan
-% % % % % % %
-Engineering 10% 88.53 61.22 -27.31 90.56 62.58 -27.98 92.87
-Procurement 40% 76.59 74.50 -2.09 78.27 75.20 -3.07 79.80
-Construction 40% 15.74 16.10 0.36 17.02 17.03 0.01 18.55
-Commissioning 10% 0 0 0 0 0 0 0
-Overall 100% 45.78 42.36 -3.42 47.17 43.15 -4.02 48.62
-Safety &amp; Health :
-• Conduct SafetyToolbox Talk before starting work.
-• Mass Safety Talk at Site Area
-• Management Walk Down every Friday (10.00 – 11.00)
-• HSE Weekly Audit every Wednesday (10.00-11.00)
-• HSE Weekly Meeting with Subcontractor every Wednesday (10.00-11.00)
-• Safety Induction Training for new comers
-• Working at height Training
-Environment &amp; CoP :
-• Water spray at construction site
-• Temporary Wheel wash station</t>
+          <t>Bunker wall concrete pouring at EL +12m.
+FGT steel structure installation</t>
         </is>
       </c>
     </row>
@@ -1092,30 +1074,7 @@
           <t>BOP Tasks that have started and those that have not yet started are behind schedule</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Safety &amp; Health:
-Management site walkdown
-Toolbox talk activity
-Safety induction training to new contractors​
-Weekly Inspect Safety​
-Weekly Random Alc. Test
-Environment &amp; CoP:
-Road cleaning (Campsite STECON/IEAT Road)
-Water spray to reduce dust
-Monitor noise during overtime work
-Activities CC/SC (*)
-Plan Actual Diff. Plan Actual Diff. Acc.Plan
-% % % % % % %
-Engineering 10.00% 76.94% 61.20% -15.75% 80.56% 62.62% -17.93% 87.84%
-Procurement 40.00% 63.35% 68.44% 5.09% 66.12% 69.13% 3.01% 68.38%
-Construction 40.00% 8.65% 8.80% 0.16% 9.45% 9.73% 0.28% 10.42%
-Commissioning 10.00% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00%
-Overall 100.00% 36.49% 37.02% 0.52% 38.28% 37.81% -0.48% 40.31%
-**Engineering Delay from O &amp; M Manual, Shop Test Report
-On Schedule A Bit Delay Big Delay</t>
-        </is>
-      </c>
+      <c r="E18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1138,30 +1097,7 @@
           <t>Bunker surround delay start affect to Boiler installation feeding gate plan.</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Safety &amp; Health:
-Management site walkdown
-Toolbox talk activity
-Safety induction training to new contractors​
-Weekly Inspect Safety​
-Weekly Random Alc. Test
-Environment &amp; CoP:
-Road cleaning (Campsite STECON/IEAT Road)
-Water spray to reduce dust
-Monitor noise during overtime work
-Activities CC/SC (*)
-Plan Actual Diff. Plan Actual Diff. Acc.Plan
-% % % % % % %
-Engineering 10.00% 88.53% 60.66% -27.87% 90.56% 62.18% -28.38% 92.87%
-Procurement 40.00% 76.59% 74.50% -2.08% 78.27% 75.20% -3.07% 79.80%
-Construction 40.00% 15.74% 12.20% -3.54% 17.02% 13.40% -3.63% 18.55%
-Commissioning 10.00% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00%
-Overall 100.00% 45.78% 40.75% -5.03% 47.17% 41.66% -5.52% 48.62%
-** Engineering delay from O &amp; M Manual, Shop Test Report , Shop ITP
-** Procurement delay from Manufacturing Boiler structure &amp; equipment and Manufacturing STG foundation anchor bolts, condenser metal sheet</t>
-        </is>
-      </c>
+      <c r="E19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1181,50 +1117,19 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>• Discussion with CEEC regarding the Bunker Building and STG &amp; ECB implementation plan.
-• Delay in Incinerator and Slag Extractor Installation Due to Material Delivery by 18 Aug 26
-Stakeholder Management
-113 Safety Weekly Audit issue status by weekly
-Total Issues 30
-Since 25 Jan 2026
-Safety Weekly Audit issue Status Chart 6 - 12 Aug
-Open Closed
-Before After
-Unsafe Action
-Already improved
-STECON :Lack of securely
-fastened to prevent them from
-falling and hitting the ground.
-Government Agencies
-Area of concern :
-Insufficient construction access roads within the site to support ongoing activities
-• Insufficient lanes in work zone.
-• The Owner will be coordinating with IEAT to secure site access for the construction road and traffic management.
-Site Boundary</t>
+          <t>Insufficient construction access roads within the site to support ongoing activities
+Site Boundary
+Access road obstruction with construction STG Building.
+Existing drainage interrupt with foundation STG building</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Jul 2026) Aug 2026)
-Activities CC/SC(*)
-Plan Actual Diff. Plan Actual Diff. Acc.Plan
-% % % % % % %
-Engineering 10% 88.53% 60.56% -27.97% 90.56% 61.96% -28.60% 92.87%
-Procurement 40% 75.59% 74.50% -1.09% 78.27% 75.20% -3.07% 79.80%
-Construction 40% 15.74% 10.63% -5.11% 17.02% 11.09% -5.93% 18.55%
-Commissioning 10% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00%
-Overall 100% 45.78% 40.11% -5.67% 47.17% 40.71% -6.46% 48.62%
-EPC has adjusted the PMS to Rev.cto make the plan consistent with the actual work.
-On Schedule A BitDelay Big Delay
-(0.00% or more) (-0.01% to –4.99%) (-5.00% or more)
-Safety &amp; Health
-• Management Weekly Route Walk - Every Tuesday
-• Weekly ESH Meeting - Every Tuesday
-• Weekly Project Meeting with - Every Tuesday
-• Toolbox Talk - Everyday before working
-• Safety training (if any)
-• Inspect equipment before working (Daily)
-• Random test alcohol</t>
+          <t>Bunker Building: Pouring concrete Lift 2 EL (+1 to +5.45) (Targeted date 6 Sep 26)
+Boiler Island:Pouring concrete slab , Pouring Concrete Reuse water pool
+FGT : Pouring concrete for ground beam , Pouring concrete footing
+STG &amp; ECB: Pouring concrete ground beam , Pouring concrete Slab&amp;Wall Miscellaneous
+Boiler &amp; Incinerator: Incinerator grate Installation ; Targeted date 28 Aug 26</t>
         </is>
       </c>
     </row>
@@ -1246,50 +1151,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>• Discussion with CEEC regarding the Bunker Building and STG &amp; ECB implementation plan.
-• Spare Parts Shipment : Pressure part Delivery to site is scheduled for 18-20 Aug 2026.
-Stakeholder Management
-132 Safety Weekly Audit issue status by weekly
-Total Issues 30
-Since 2 Jan 2026 10
-6 - 12 August
-Safety Weekly Audit issue Status Chart
-Open Closed
-Before After
-Unsafe Condition Already improve
-STECON : Hard barricade
-had collapsed
-Government Agencies
-Problem : Electric Pole obstruct Entrance
-ตําแหน่งเสาไฟฟ้าเดิม
-N.= 1602494.440
-E.= 671208.496
-Entrance ตําแหน่งเสาไฟฟ้าใหม่
- ทําหนังสอื แจง้ ทาง กนอ &gt;&gt; กนอทําหนังสอื แจง้ ทาง PEA &gt;&gt; PEA นครหลวง รบั เรอ(cid:341)ื งดําเนินการต่อ</t>
+          <t>Problem : Electric Pole obstruct Entrance</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Jul 2026) Aug 2026)
-Activities CC/SC(*)
-Plan Actual Diff. Plan Actual Diff. Acc.Plan
-% % % % % % %
-Engineering 10% 92.82% 61.01% -31.81% 93.44% 62.69% -30.75% 94.92%
-Procurement 40% 82.61% 79.02% -3.59% 84.27% 79.50% -4.77% 79.50%
-Construction 40% 22.90% 14.08% -8.82% 25.06% 14.90% -10.16% 14.90%
-Commissioning 10% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00%
-Overall 100% 51.49% 43.34% -8.15% 53.08% 44.03% -9.05% 44.03%
-EPC has adjusted the PMS to Rev.Cto make the plan consistent with the actual work.
-On Schedule A BitDelay Big Delay
-(0.00% or more) (-0.01% to –4.99%) (-5.00% or more)
-Safety &amp; Health
-• Management Weekly Route Walk - Every Tuesday
-• Weekly ESH Meeting - Every Tuesday
-• Weekly Project Meeting with - Every Tuesday
-• Toolbox Talk - Everyday before working
-• Safety training (if any)
-• Inspect equipment before working (Daily)
-• Random test alcohol</t>
+          <t>Bunker Building: Lift 2 (EL. +1.0 to +5.45) ; Targeted date 24 Aug 26
+Boiler Island:Pouring concrete slab on ground (Z1-Z6)
+FGT : Pouring concrete for tie beam
+STG &amp; ECB: Pouring concrete Slab EL +0.25 &amp; Column
+Boiler &amp; Incinerator: Completion of Boiler Drum Installation. ; Targeted date 25 Aug 26
+BOP : Commence foundation work for BOP</t>
         </is>
       </c>
     </row>
@@ -1311,50 +1183,14 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>333 Boiler Foundation - Boiler Island 1 May 26 26 June 26 21 May 26 5 Jul 26 Completed
-334 Clearance for boiler installation- Boiler Island 27 June 26 4 July 26 21 May 26 5 Jul 26 Completed
-Piling Work(Including Pile test)- Flue Gas Treatment
-342 2 May 26 30 May 26 4 May 26 19 May 26 Completed
-Equipment Foundation
-Foundation work - Flue Gas Treatment Equipment
-344 11 June 26 21 Aug 26 21 May 26 31 Jul 26 Completed
-Safety Weekly Audit issue status by weekly
-Total Issues 40
-Since 2 Apr 2026
-0 0 0 0 0 0 0
-Safety Weekly Audit issue Status Chart
-Open Closed
-BOP Drawing still not approve
-Service water tank storages – Waiting OE review
-Cooling tower – Waiting OE review
-Demin water treatment plant – Waiting OE review
-Fire water pump shelter – NE Status Waiting return to CEEC
-Transformer
-• 13 Aug 26: CEEC update drawing to Stecon</t>
+          <t>Service Water &amp; Firefighting Tank DWG. For order material.
+Request CEEC to Order material fire fighting underground and aboveground piping.</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Safety &amp; Health:
-• Safety Toolbox Talk before starting work and Mass Safety Talk.
-• Safety induction training.
-• Tools and equipment’s inspection.
-• Management walkdown.
-• Random alcohol test.
-• Random drug test.
-Environment &amp; CoP:
-• Water spray to reduce dust.
-• Wheel washing before entering public road.
-• Road cleaning.
-• Install rebar and pouring concrete wall +6.65 to +7.85 m.
-• Install rebar and pouring concrete wall +7.85 to +9.05 m.
-• Install rebar and pouring concrete wall +9.05 to +10.25 m.
-• Adjust formwork (Close opening)
-• Remove scaffolding and peri platform
-EL +6.65 m Problem: -
-Activity wall Qty total Qty complete %Complete
-Wall rebar +5.45 to +6.65 m. 4 side 4 side 100.00%
-Slipform installation 12 set 12 Set 100.00%</t>
+          <t>Work Foundation at Bunker to 18.00 m
+Work Foundation at Boiler, FGT, STG area</t>
         </is>
       </c>
     </row>
@@ -1376,50 +1212,15 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>105 Safety Weekly Audit issue status by weekly
-Total Issues
-Since 2 Apr 2026 20
-0 0 0 0 0 0 0
-Safety Weekly Audit issue Status Chart
-0 Open Closed
-Open Closed
-BEFORE AFTER
-Retaining wall (River side) – Stecon scope of work and submit Quotation to CEEC
-• Affect BOP building construction activity
-BOP Drawing still not approve
-Service water tank storages – Waiting OE review
-Cooling tower – Waiting OE review
-Demin water treatment plant – Waiting OE review
-Fire water pump shelter - Waiting OE review and SEPEC update cal.
-Transformer – No calculation for OE review process (Within 15 Aug 26)
-Raw water treatment plant - No drawing (Within (15 Aug 26)
-Property Boundary
-The permanent fence concept on the south side.
-Circulating and Firefighting Underground pipes are required long lead for fabrication and delivery from manufacturer. CEEC</t>
+          <t>Contractor for Retaining wall south side
+Service Water &amp; Firefighting Tank DWG. For order material.
+Request CEEC to Order material fire fighting underground and aboveground piping.</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Safety &amp; Health:
-• Safety Toolbox Talk before starting work and Mass Safety Talk.
-• Safety induction training.
-• Tools and equipment’s inspection.
-• Management walkdown.
-• Random alcohol test.
-• Random drug test.
-Environment &amp; CoP:
-• Water spray to reduce dust.
-• Wheel washing before entering public road.
-• Road cleaning.
-• Continuous pouring concrete with slipform +6.65 m.
-• Continuous pouring concrete with slipform +7.85 m.
-• Continuous pouring concrete with slipform +9.05 m.
-• Adjust formwork (Close opening)
-Activity wall Qty total Qty complete %Complete
-Concrete wall +5.45 m. 40 cu.m. 40 cu.m. 100.00%
-Concrete wall +6.65 m. 40 cu.m. 0 cu.m. 0.00%
-Concrete wall +7.85 m. 40 cu.m. 0 cu.m. 0.00%
-• Continuous ground beam work</t>
+          <t>1. Work Foundation at Bunker to 18.00 m
+Work Foundation at Boiler, FGT, STG area</t>
         </is>
       </c>
     </row>
@@ -1441,31 +1242,15 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Skill manpower shortage e.g. fitter, piping welder</t>
+          <t>Skill manpower shortage e.g. fitter, piping welder
+Recommend spare part list
+Isometric drawing of fire fighting system (U/G and A/G).
+Pipe support standard drawing from CEEC.</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>(07 Aug 26) (14 Aug 26)
-Activities CC/SC (*)
-Plan Actual Diff. Plan Actual Diff. Acc.Plan
-% % % % % % %
-Engineering 10% 92.82 60.78 -32.04 93.44 62.26 -31.18 94.92
-Procurement 40% 82.61 79.02 -3.59 84.27 79.50 -4.77 85.67
-Construction 40% 22.90 18.13 -4.77 25.06 20.37 -4.69 27.18
-Commissioning 10% 0 0 0 0 0 0 0
-Overall 100% 51.49 44.94 -6.55 53.08 46.17 -6.91 54.63
-Safety &amp; Health :
-• Conduct SafetyToolbox Talk before starting work.
-• Mass Safety Talk at Site Area
-• Management Walk Down every Friday (10.00 – 11.00)
-• HSE Weekly Audit every Wednesday (10.00-11.00)
-• HSE Weekly Meeting with Subcontractor every Wednesday (10.00-11.00)
-• Safety Induction Training for new comers
-• Working at height Training
-Environment &amp; CoP :
-• Water spray at construction site
-• Temporary Wheel wash station</t>
+          <t>Tie beam works at EL+8m of bunker building 2. Water Wall installation</t>
         </is>
       </c>
     </row>
@@ -1490,31 +1275,15 @@
           <t>Detail and spec of equipment at riser pole for PEA approval.
 Detail drawing of water pond.
 Detail drawing of pump foundation at cooling, service water pump
-Detail drawing of foundation and architecture of BOP building</t>
+Detail drawing of foundation and architecture of BOP building . Detail of underground pipe of toilet at steam turbine building.</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>Activities CC/SC (*)
-Plan% Actual% Diff.% Plan% Actual% Diff.% Acc. Plan%
-Engineering 10% 93.75% 64.67% -29.08% 94.23% 66.07% -28.16% 95.68%
-Procurement 40% 87.53% 80.40% -7.13% 88.85% 80.77% -8.08% 89.99%
-Construction 40% 27.12% 19.55% -7.57% 28.97% 20.84% -8.13% 31.24%
-Commissioning 10% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00% 0.00%
-Overall 100% 55.23% 46.45% -8.78% 56.55% 47.25% -9.30% 58.06%
-5 Maximum Quantity of Heavy Machinery at Site Inspection as period
-and keep related document
-6 Summary of SHE Weekly Audit issues Walk down
-- This week (Finished : 6, Remaining : 0)
-- Total (Finished : 102, Remaining : 0)
-0 RFC , 3 NCR
-7 Stakeholder Engagement Plan Continue as plan
-8 SHE Plan for counting manpower working at site Able to be facial scan 100% (Manpower daily report havealready
-started to generating automatically at 7:00 AM everyday by e-mail
-9 Status of EPC Foreigner staff and worker personal mandatory document Pending has plan to finish &lt;31 Aug 2026&gt;
-Safety &amp; Health:
-• Safety Toolbox Talk before starting work and Mass Toolbox Talk and counting manpower
-• Safety training for newcomer</t>
+          <t>Pouring concrete by slip from method From EL.+8.0 to +18.30 m.
+Boiler: Install boiler wall.
+FGT: Install reactor tower and structure.
+STG : Column for second floor at EL +3.70 m</t>
         </is>
       </c>
     </row>
@@ -1534,67 +1303,64 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>No. Description Progress Remark
-Contractor submitted the Contractor’s
-The contractor has appointed persons to all positions of key personnel and provided a
-representative proposal for the
-detailed organization chart to the employer before the commencement of LNTP works,
-1 Employer’s review. And key
-and for this purpose sub-clause 6.12 of the general conditions shall apply mutatis
-personnel and organization are also
-submitted for review.
-The EPC contractor has sorted out a total of 38 types of permits required for the
-contract to take effect and 33 have been completed.
-No Issue Detail Action by Target ate Progress Remark
-EPC shall maintain alignment of progress reporting,
-Project Master EPC has maintained alighment of progress reporting
-1 S-curve monitoring and forecasting with the EPC Immediate
-Schedule and S curve with the approved baseline
-approved Project Master Schedule.
-EPC shall continue weekly submission of the
-2 Prioritized list prioritized list of drawings, reports and critical EPC Ongoing Noted
-deliverables.</t>
-        </is>
-      </c>
+      <c r="D26" s="2" t="inlineStr"/>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>List of Issues to be Coordinated
-Planned (%) (%)
-Design Works 0.404% 17.14% 0.804% 17.946% 0.404% 18.350% 0.404% 18.754%
-Procurement,
-Production &amp; 0.386% 6.73% 0.773% 7.501% 0.386% 7.887% 0.386% 8.274%
-Preparatory
-705% 37.20% 0.605% 37.80% 0.705% 38.505% 0.705% 39.210%
-614% 22.70% 0.614% 23.31% 0.614% 23.927% 0.614% 24.541%
-Construction
-Water Diversion 0.000% 0.00% 0.000% 0.000% 0.000% 0.000% 0.000% 0.000%
-430% 8.44% 0.430% 8.870% 0.430% 9.299% 0.430% 9.729%
-Phase 1 &amp; 2
-PROGRESS 0.193% 4.84% 0.193% 5.06% 0.193% 5.23% 0.193% 5.45%
-(Cumulative %)</t>
+          <t>[EPC Hub Camp] R etaining wall concrete pouring(#1) — 12 m3
+[EPC Hub Camp] Installation of reinforced stone cages — 100 Pcs
+[EPC Hub Camp] Site hardening(#2~#5) — 600 m2
+[EPC Hub Camp] Portable house installation(office) — 154 m2
+[Construction Management Camp] Installation of wastewater treatment equipment — 0.5 Item
+[Labour Camp] Portable house foundation concrete pouring (1 buildings) — 18 m3
+[Labour Camp] Portable house installation (6 buildings) — 1200 m3
+[Labour Camp] Site hardening — 1000 m2
+[Left Bank Aggregate &amp; Batching System] Construction of slop berm drainage channel — 100 m
+[Left Bank Aggregate &amp; Batching System] Site hardening for finished product silo — 1000 m2
+[Left Bank Aggregate &amp; Batching System] Conveyor belt concrete pouring — 293 m3
+[Left Bank Aggregate &amp; Batching System] Substation foundation concrete pouring — 25 m3
+[Left Bank Aggregate &amp; Batching System] Concrete pouring in the drying workshop — 75 m3
+[Left Bank Aggregate &amp; Batching System] Construction of drainage channel for finished product silo — 260 m
+[Left Bank Aggregate &amp; Batching System] #1 installation of the ice-making building — 0.18 Item
+[Left Bank Aggregate &amp; Batching System] #5~#8 Ash tanks installation — 0.5 Item
+[Left Bank Aggregate &amp; Batching System] #1~#9 Tape conveyor column installation — 0.5 Item
+[Access Road] R o ad #6 hardening — 200 m
+[Access Road] Slab culvert base slab and side wall concrete at Road #1 K0+835 — 200 m3
+[Access Road] Backfilling for Road #2 K0+20-K0+60 — 4900 m3</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>PRJ-026</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>Pak Beng</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="inlineStr"/>
-      <c r="E27" s="3" t="inlineStr"/>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Earth‑ rock Excavation — 10000 m³ (2.71%)
+EL.364~379 Slope Support — 0.02 Item (2.00%)
+EL.349~364m Slope Support — 0.005 Item (0.50%)
+Grid beams with vegetation — 0.1 Item (10.00%)
+D/S approach channel above EL. 349 Grid Beam — 103 m (1.10%)
+EL.342~357 Slope Support — 0.15 Item (15.00%)
+Grid beams with vegetation — 0.2 Item (20.00%)
+Drainage Channel Base Slab — 60 m (3.01%)
+Drainage Channel Side Wall — 110 m (5.52%)
+1# chute bottom slab concrete — 46 m (31.23%)
+2# chute support — 0.2 Item (20.00%)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
